--- a/NARI_Model.xlsx
+++ b/NARI_Model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5405CF9A-E7DE-43C4-9E85-5EF081ED72C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79B4E5F-264C-43BE-93E2-44412CAFAE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,8 @@
   <externalReferences>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2868,24 +2870,6 @@
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="2" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2898,6 +2882,12 @@
     <xf numFmtId="10" fontId="2" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2907,10 +2897,25 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2919,10 +2924,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8184,6 +8186,67 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>11204</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>593912</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="dimg_zX4-afm1LefFp84PrbSBqQU_15" descr="Inari Medical - YouTube">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EEB1791-BA5A-7E23-B125-6185EA54D534}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="13144" b="14301"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3765177" y="571498"/>
+          <a:ext cx="1792941" cy="1266268"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9621,6 +9684,878 @@
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Notes | Quant Analysis"/>
+      <sheetName val="M&amp;A"/>
+      <sheetName val="Management"/>
+      <sheetName val="Markets | Product Lines"/>
+      <sheetName val="Debt Schedule"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="AY1" t="str">
+            <v>Q1 2021</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AW4">
+            <v>467</v>
+          </cell>
+          <cell r="AX4">
+            <v>555</v>
+          </cell>
+          <cell r="AY4">
+            <v>469</v>
+          </cell>
+          <cell r="AZ4">
+            <v>517</v>
+          </cell>
+          <cell r="BA4">
+            <v>525</v>
+          </cell>
+          <cell r="BB4">
+            <v>600</v>
+          </cell>
+          <cell r="BC4">
+            <v>528</v>
+          </cell>
+          <cell r="BD4">
+            <v>563</v>
+          </cell>
+          <cell r="BE4">
+            <v>535</v>
+          </cell>
+          <cell r="BF4">
+            <v>653</v>
+          </cell>
+          <cell r="BG4">
+            <v>566</v>
+          </cell>
+          <cell r="BH4">
+            <v>622</v>
+          </cell>
+          <cell r="BI4">
+            <v>620</v>
+          </cell>
+          <cell r="BJ4">
+            <v>726</v>
+          </cell>
+          <cell r="BK4">
+            <v>667</v>
+          </cell>
+          <cell r="BL4">
+            <v>698</v>
+          </cell>
+          <cell r="BM4">
+            <v>679</v>
+          </cell>
+          <cell r="BN4">
+            <v>790</v>
+          </cell>
+          <cell r="BO4">
+            <v>730</v>
+          </cell>
+          <cell r="BP4"/>
+          <cell r="BQ4"/>
+        </row>
+        <row r="5">
+          <cell r="AW5">
+            <v>467</v>
+          </cell>
+          <cell r="AX5">
+            <v>525</v>
+          </cell>
+          <cell r="AY5">
+            <v>469</v>
+          </cell>
+          <cell r="AZ5">
+            <v>518</v>
+          </cell>
+          <cell r="BA5">
+            <v>525</v>
+          </cell>
+          <cell r="BB5">
+            <v>629</v>
+          </cell>
+          <cell r="BC5">
+            <v>538</v>
+          </cell>
+          <cell r="BD5">
+            <v>600</v>
+          </cell>
+          <cell r="BE5">
+            <v>590</v>
+          </cell>
+          <cell r="BF5">
+            <v>997</v>
+          </cell>
+          <cell r="BG5">
+            <v>707</v>
+          </cell>
+          <cell r="BH5">
+            <v>713</v>
+          </cell>
+          <cell r="BI5">
+            <v>746</v>
+          </cell>
+          <cell r="BJ5">
+            <v>902</v>
+          </cell>
+          <cell r="BK5">
+            <v>778</v>
+          </cell>
+          <cell r="BL5">
+            <v>768</v>
+          </cell>
+          <cell r="BM5">
+            <v>837</v>
+          </cell>
+          <cell r="BN5">
+            <v>1006</v>
+          </cell>
+          <cell r="BO5">
+            <v>867</v>
+          </cell>
+          <cell r="BP5"/>
+          <cell r="BQ5"/>
+        </row>
+        <row r="6">
+          <cell r="AW6">
+            <v>600</v>
+          </cell>
+          <cell r="AX6">
+            <v>705</v>
+          </cell>
+          <cell r="AY6">
+            <v>622</v>
+          </cell>
+          <cell r="AZ6">
+            <v>640</v>
+          </cell>
+          <cell r="BA6">
+            <v>636</v>
+          </cell>
+          <cell r="BB6">
+            <v>709</v>
+          </cell>
+          <cell r="BC6">
+            <v>664</v>
+          </cell>
+          <cell r="BD6">
+            <v>666</v>
+          </cell>
+          <cell r="BE6">
+            <v>765</v>
+          </cell>
+          <cell r="BF6">
+            <v>936</v>
+          </cell>
+          <cell r="BG6">
+            <v>778</v>
+          </cell>
+          <cell r="BH6">
+            <v>841</v>
+          </cell>
+          <cell r="BI6">
+            <v>798</v>
+          </cell>
+          <cell r="BJ6">
+            <v>1042</v>
+          </cell>
+          <cell r="BK6">
+            <v>864</v>
+          </cell>
+          <cell r="BL6">
+            <v>908</v>
+          </cell>
+          <cell r="BM6">
+            <v>938</v>
+          </cell>
+          <cell r="BN6">
+            <v>1142</v>
+          </cell>
+          <cell r="BO6">
+            <v>945</v>
+          </cell>
+          <cell r="BP6"/>
+          <cell r="BQ6"/>
+        </row>
+        <row r="7">
+          <cell r="AW7">
+            <v>66</v>
+          </cell>
+          <cell r="AX7">
+            <v>82</v>
+          </cell>
+          <cell r="AY7">
+            <v>289</v>
+          </cell>
+          <cell r="AZ7">
+            <v>301</v>
+          </cell>
+          <cell r="BA7">
+            <v>295</v>
+          </cell>
+          <cell r="BB7">
+            <v>303</v>
+          </cell>
+          <cell r="BC7">
+            <v>301</v>
+          </cell>
+          <cell r="BD7">
+            <v>306</v>
+          </cell>
+          <cell r="BE7">
+            <v>294</v>
+          </cell>
+          <cell r="BF7">
+            <v>299</v>
+          </cell>
+          <cell r="BG7">
+            <v>284</v>
+          </cell>
+          <cell r="BH7">
+            <v>311</v>
+          </cell>
+          <cell r="BI7">
+            <v>311</v>
+          </cell>
+          <cell r="BJ7">
+            <v>320</v>
+          </cell>
+          <cell r="BK7">
+            <v>310</v>
+          </cell>
+          <cell r="BL7">
+            <v>327</v>
+          </cell>
+          <cell r="BM7">
+            <v>329</v>
+          </cell>
+          <cell r="BN7">
+            <v>341</v>
+          </cell>
+          <cell r="BO7">
+            <v>406</v>
+          </cell>
+          <cell r="BP7"/>
+          <cell r="BQ7"/>
+        </row>
+        <row r="8">
+          <cell r="AW8">
+            <v>518</v>
+          </cell>
+          <cell r="AX8">
+            <v>312</v>
+          </cell>
+          <cell r="AY8">
+            <v>281</v>
+          </cell>
+          <cell r="AZ8">
+            <v>310</v>
+          </cell>
+          <cell r="BA8">
+            <v>299</v>
+          </cell>
+          <cell r="BB8">
+            <v>324</v>
+          </cell>
+          <cell r="BC8">
+            <v>323</v>
+          </cell>
+          <cell r="BD8">
+            <v>337</v>
+          </cell>
+          <cell r="BE8">
+            <v>332</v>
+          </cell>
+          <cell r="BF8">
+            <v>384</v>
+          </cell>
+          <cell r="BG8">
+            <v>355</v>
+          </cell>
+          <cell r="BH8">
+            <v>373</v>
+          </cell>
+          <cell r="BI8">
+            <v>384</v>
+          </cell>
+          <cell r="BJ8">
+            <v>764</v>
+          </cell>
+          <cell r="BK8">
+            <v>478</v>
+          </cell>
+          <cell r="BL8">
+            <v>416</v>
+          </cell>
+          <cell r="BM8">
+            <v>441</v>
+          </cell>
+          <cell r="BN8">
+            <v>801</v>
+          </cell>
+          <cell r="BO8">
+            <v>563</v>
+          </cell>
+          <cell r="BP8"/>
+          <cell r="BQ8"/>
+        </row>
+        <row r="10">
+          <cell r="AW10">
+            <v>435</v>
+          </cell>
+          <cell r="AX10">
+            <v>459</v>
+          </cell>
+          <cell r="AY10">
+            <v>412</v>
+          </cell>
+          <cell r="AZ10">
+            <v>474</v>
+          </cell>
+          <cell r="BA10">
+            <v>439</v>
+          </cell>
+          <cell r="BB10">
+            <v>523</v>
+          </cell>
+          <cell r="BC10">
+            <v>464</v>
+          </cell>
+          <cell r="BD10">
+            <v>500</v>
+          </cell>
+          <cell r="BE10">
+            <v>481</v>
+          </cell>
+          <cell r="BF10">
+            <v>552</v>
+          </cell>
+          <cell r="BG10">
+            <v>566</v>
+          </cell>
+          <cell r="BH10">
+            <v>562</v>
+          </cell>
+          <cell r="BI10">
+            <v>515</v>
+          </cell>
+          <cell r="BJ10">
+            <v>630</v>
+          </cell>
+          <cell r="BK10">
+            <v>588</v>
+          </cell>
+          <cell r="BL10">
+            <v>602</v>
+          </cell>
+          <cell r="BM10">
+            <v>570</v>
+          </cell>
+          <cell r="BN10">
+            <v>687</v>
+          </cell>
+          <cell r="BO10">
+            <v>639</v>
+          </cell>
+          <cell r="BP10"/>
+          <cell r="BQ10"/>
+        </row>
+        <row r="11">
+          <cell r="AW11">
+            <v>334</v>
+          </cell>
+          <cell r="AX11">
+            <v>340</v>
+          </cell>
+          <cell r="AY11">
+            <v>309</v>
+          </cell>
+          <cell r="AZ11">
+            <v>353</v>
+          </cell>
+          <cell r="BA11">
+            <v>328</v>
+          </cell>
+          <cell r="BB11">
+            <v>352</v>
+          </cell>
+          <cell r="BC11">
+            <v>327</v>
+          </cell>
+          <cell r="BD11">
+            <v>364</v>
+          </cell>
+          <cell r="BE11">
+            <v>347</v>
+          </cell>
+          <cell r="BF11">
+            <v>375</v>
+          </cell>
+          <cell r="BG11">
+            <v>375</v>
+          </cell>
+          <cell r="BH11">
+            <v>393</v>
+          </cell>
+          <cell r="BI11">
+            <v>362</v>
+          </cell>
+          <cell r="BJ11">
+            <v>414</v>
+          </cell>
+          <cell r="BK11">
+            <v>393</v>
+          </cell>
+          <cell r="BL11">
+            <v>428</v>
+          </cell>
+          <cell r="BM11">
+            <v>420</v>
+          </cell>
+          <cell r="BN11">
+            <v>463</v>
+          </cell>
+          <cell r="BO11">
+            <v>443</v>
+          </cell>
+          <cell r="BP11"/>
+          <cell r="BQ11"/>
+        </row>
+        <row r="12">
+          <cell r="AW12">
+            <v>430</v>
+          </cell>
+          <cell r="AX12">
+            <v>570</v>
+          </cell>
+          <cell r="AY12">
+            <v>640</v>
+          </cell>
+          <cell r="AZ12">
+            <v>674</v>
+          </cell>
+          <cell r="BA12">
+            <v>639</v>
+          </cell>
+          <cell r="BB12">
+            <v>711</v>
+          </cell>
+          <cell r="BC12">
+            <v>685</v>
+          </cell>
+          <cell r="BD12">
+            <v>676</v>
+          </cell>
+          <cell r="BE12">
+            <v>672</v>
+          </cell>
+          <cell r="BF12">
+            <v>774</v>
+          </cell>
+          <cell r="BG12">
+            <v>769</v>
+          </cell>
+          <cell r="BH12">
+            <v>766</v>
+          </cell>
+          <cell r="BI12">
+            <v>752</v>
+          </cell>
+          <cell r="BJ12">
+            <v>860</v>
+          </cell>
+          <cell r="BK12">
+            <v>830</v>
+          </cell>
+          <cell r="BL12">
+            <v>832</v>
+          </cell>
+          <cell r="BM12">
+            <v>849</v>
+          </cell>
+          <cell r="BN12">
+            <v>996</v>
+          </cell>
+          <cell r="BO12">
+            <v>945</v>
+          </cell>
+          <cell r="BP12"/>
+          <cell r="BQ12"/>
+        </row>
+        <row r="13">
+          <cell r="AW13">
+            <v>302</v>
+          </cell>
+          <cell r="AX13">
+            <v>307</v>
+          </cell>
+          <cell r="AY13">
+            <v>278</v>
+          </cell>
+          <cell r="AZ13">
+            <v>307</v>
+          </cell>
+          <cell r="BA13">
+            <v>282</v>
+          </cell>
+          <cell r="BB13">
+            <v>300</v>
+          </cell>
+          <cell r="BC13">
+            <v>279</v>
+          </cell>
+          <cell r="BD13">
+            <v>290</v>
+          </cell>
+          <cell r="BE13">
+            <v>280</v>
+          </cell>
+          <cell r="BF13">
+            <v>297</v>
+          </cell>
+          <cell r="BG13">
+            <v>284</v>
+          </cell>
+          <cell r="BH13">
+            <v>296</v>
+          </cell>
+          <cell r="BI13">
+            <v>291</v>
+          </cell>
+          <cell r="BJ13">
+            <v>122</v>
+          </cell>
+          <cell r="BK13">
+            <v>171</v>
+          </cell>
+          <cell r="BL13">
+            <v>307</v>
+          </cell>
+          <cell r="BM13">
+            <v>304</v>
+          </cell>
+          <cell r="BN13">
+            <v>85</v>
+          </cell>
+          <cell r="BO13">
+            <v>166</v>
+          </cell>
+          <cell r="BP13"/>
+          <cell r="BQ13"/>
+        </row>
+        <row r="14">
+          <cell r="AW14">
+            <v>118</v>
+          </cell>
+          <cell r="AX14">
+            <v>157</v>
+          </cell>
+          <cell r="AY14">
+            <v>123</v>
+          </cell>
+          <cell r="AZ14">
+            <v>127</v>
+          </cell>
+          <cell r="BA14">
+            <v>123</v>
+          </cell>
+          <cell r="BB14">
+            <v>176</v>
+          </cell>
+          <cell r="BC14">
+            <v>97</v>
+          </cell>
+          <cell r="BD14">
+            <v>114</v>
+          </cell>
+          <cell r="BE14">
+            <v>111</v>
+          </cell>
+          <cell r="BF14">
+            <v>153</v>
+          </cell>
+          <cell r="BG14">
+            <v>94</v>
+          </cell>
+          <cell r="BH14">
+            <v>119</v>
+          </cell>
+          <cell r="BI14">
+            <v>130</v>
+          </cell>
+          <cell r="BJ14">
+            <v>35</v>
+          </cell>
+          <cell r="BK14">
+            <v>164</v>
+          </cell>
+          <cell r="BL14">
+            <v>136</v>
+          </cell>
+          <cell r="BM14">
+            <v>127</v>
+          </cell>
+          <cell r="BN14">
+            <v>125</v>
+          </cell>
+          <cell r="BO14">
+            <v>162</v>
+          </cell>
+          <cell r="BP14"/>
+          <cell r="BQ14"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="188">
+          <cell r="I188" t="str">
+            <v>Notes:</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main | Overview"/>
+      <sheetName val="Model"/>
+      <sheetName val="Notes | Quant Analysis"/>
+      <sheetName val="M&amp;A Scope"/>
+      <sheetName val="Markets | Product Lines"/>
+      <sheetName val="Management"/>
+      <sheetName val="Debt Schedule"/>
+      <sheetName val="Clinical Trial Channel"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="AW3" t="str">
+            <v>Q1 2020</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="AW50">
+            <v>2543</v>
+          </cell>
+          <cell r="AX50">
+            <v>2003</v>
+          </cell>
+          <cell r="AY50">
+            <v>2659</v>
+          </cell>
+          <cell r="AZ50">
+            <v>2708</v>
+          </cell>
+          <cell r="BA50">
+            <v>2752</v>
+          </cell>
+          <cell r="BB50">
+            <v>3077</v>
+          </cell>
+          <cell r="BC50">
+            <v>2932</v>
+          </cell>
+          <cell r="BD50">
+            <v>3127</v>
+          </cell>
+          <cell r="BE50">
+            <v>3026</v>
+          </cell>
+          <cell r="BF50">
+            <v>3244</v>
+          </cell>
+          <cell r="BG50">
+            <v>3170</v>
+          </cell>
+          <cell r="BH50">
+            <v>3242</v>
+          </cell>
+          <cell r="BI50">
+            <v>3389</v>
+          </cell>
+          <cell r="BJ50">
+            <v>3599</v>
+          </cell>
+          <cell r="BK50">
+            <v>3527</v>
+          </cell>
+          <cell r="BL50">
+            <v>3725</v>
+          </cell>
+          <cell r="BM50">
+            <v>3857</v>
+          </cell>
+          <cell r="BN50">
+            <v>4120</v>
+          </cell>
+          <cell r="BO50">
+            <v>4209</v>
+          </cell>
+          <cell r="BP50">
+            <v>4561</v>
+          </cell>
+          <cell r="BQ50">
+            <v>4663</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="AW70">
+            <v>11</v>
+          </cell>
+          <cell r="AX70">
+            <v>-152</v>
+          </cell>
+          <cell r="AY70">
+            <v>-169</v>
+          </cell>
+          <cell r="AZ70">
+            <v>196</v>
+          </cell>
+          <cell r="BA70">
+            <v>327</v>
+          </cell>
+          <cell r="BB70">
+            <v>172</v>
+          </cell>
+          <cell r="BC70">
+            <v>405</v>
+          </cell>
+          <cell r="BD70">
+            <v>80</v>
+          </cell>
+          <cell r="BE70">
+            <v>97</v>
+          </cell>
+          <cell r="BF70">
+            <v>246</v>
+          </cell>
+          <cell r="BG70">
+            <v>174</v>
+          </cell>
+          <cell r="BH70">
+            <v>124</v>
+          </cell>
+          <cell r="BI70">
+            <v>300</v>
+          </cell>
+          <cell r="BJ70">
+            <v>261</v>
+          </cell>
+          <cell r="BK70">
+            <v>504</v>
+          </cell>
+          <cell r="BL70">
+            <v>504</v>
+          </cell>
+          <cell r="BM70">
+            <v>495</v>
+          </cell>
+          <cell r="BN70">
+            <v>324</v>
+          </cell>
+          <cell r="BO70">
+            <v>468</v>
+          </cell>
+          <cell r="BP70">
+            <v>565</v>
+          </cell>
+          <cell r="BQ70">
+            <v>674</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="AZ115">
+            <v>1.4515077424612877</v>
+          </cell>
+          <cell r="BA115">
+            <v>1.3834364868847628</v>
+          </cell>
+          <cell r="BB115">
+            <v>1.3083722072182666</v>
+          </cell>
+          <cell r="BC115">
+            <v>1.1499254102436598</v>
+          </cell>
+          <cell r="BD115">
+            <v>1.1015679850222326</v>
+          </cell>
+          <cell r="BE115">
+            <v>0.77889564810481982</v>
+          </cell>
+          <cell r="BF115">
+            <v>0.85784187483904195</v>
+          </cell>
+          <cell r="BG115">
+            <v>0.94561848408002258</v>
+          </cell>
+          <cell r="BH115">
+            <v>1.0236655272153563</v>
+          </cell>
+          <cell r="BI115">
+            <v>0.89468528043105555</v>
+          </cell>
+          <cell r="BJ115">
+            <v>0.79701885138097328</v>
+          </cell>
+          <cell r="BK115">
+            <v>0.89561039528281283</v>
+          </cell>
+          <cell r="BL115">
+            <v>0.8169841913254966</v>
+          </cell>
+          <cell r="BM115">
+            <v>1.1438161106590725</v>
+          </cell>
+          <cell r="BN115">
+            <v>1.144906743185079</v>
+          </cell>
+          <cell r="BO115">
+            <v>1.016579259008628</v>
+          </cell>
+          <cell r="BP115">
+            <v>0.64223194748358858</v>
+          </cell>
+          <cell r="BQ115">
+            <v>0.88335310399367339</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10167,7 +11102,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:78">
+    <row r="5" spans="1:78" ht="15">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -10177,6 +11112,7 @@
       <c r="D5" s="43" t="s">
         <v>95</v>
       </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:78">
       <c r="B6" s="1" t="s">
@@ -10253,10 +11189,10 @@
       </c>
     </row>
     <row r="15" spans="1:78" ht="15" customHeight="1">
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="86"/>
+      <c r="C15" s="95"/>
       <c r="G15" s="1" t="s">
         <v>97</v>
       </c>
@@ -10361,130 +11297,130 @@
       <c r="D28" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="86" t="s">
+      <c r="F28" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="G28" s="86"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="86"/>
-      <c r="M28" s="86"/>
-      <c r="N28" s="86"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="86"/>
-      <c r="S28" s="86"/>
-      <c r="T28" s="86"/>
-      <c r="U28" s="86"/>
-      <c r="V28" s="86"/>
+      <c r="G28" s="95"/>
+      <c r="H28" s="95"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="95"/>
+      <c r="P28" s="95"/>
+      <c r="Q28" s="95"/>
+      <c r="R28" s="95"/>
+      <c r="S28" s="95"/>
+      <c r="T28" s="95"/>
+      <c r="U28" s="95"/>
+      <c r="V28" s="95"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="86"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="86"/>
-      <c r="M29" s="86"/>
-      <c r="N29" s="86"/>
-      <c r="O29" s="86"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="86"/>
-      <c r="R29" s="86"/>
-      <c r="S29" s="86"/>
-      <c r="T29" s="86"/>
-      <c r="U29" s="86"/>
-      <c r="V29" s="86"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="95"/>
+      <c r="O29" s="95"/>
+      <c r="P29" s="95"/>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="95"/>
+      <c r="S29" s="95"/>
+      <c r="T29" s="95"/>
+      <c r="U29" s="95"/>
+      <c r="V29" s="95"/>
     </row>
     <row r="30" spans="1:22">
       <c r="D30" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F30" s="86" t="s">
+      <c r="F30" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="G30" s="86"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
-      <c r="M30" s="86"/>
-      <c r="N30" s="86"/>
-      <c r="O30" s="86"/>
-      <c r="P30" s="86"/>
-      <c r="Q30" s="86"/>
-      <c r="R30" s="86"/>
-      <c r="S30" s="86"/>
-      <c r="T30" s="86"/>
-      <c r="U30" s="86"/>
-      <c r="V30" s="86"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="95"/>
+      <c r="T30" s="95"/>
+      <c r="U30" s="95"/>
+      <c r="V30" s="95"/>
     </row>
     <row r="31" spans="1:22">
-      <c r="F31" s="86"/>
-      <c r="G31" s="86"/>
-      <c r="H31" s="86"/>
-      <c r="I31" s="86"/>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
-      <c r="M31" s="86"/>
-      <c r="N31" s="86"/>
-      <c r="O31" s="86"/>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="86"/>
-      <c r="R31" s="86"/>
-      <c r="S31" s="86"/>
-      <c r="T31" s="86"/>
-      <c r="U31" s="86"/>
-      <c r="V31" s="86"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="95"/>
+      <c r="P31" s="95"/>
+      <c r="Q31" s="95"/>
+      <c r="R31" s="95"/>
+      <c r="S31" s="95"/>
+      <c r="T31" s="95"/>
+      <c r="U31" s="95"/>
+      <c r="V31" s="95"/>
     </row>
     <row r="32" spans="1:22">
       <c r="D32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="86" t="s">
+      <c r="F32" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="86"/>
-      <c r="N32" s="86"/>
-      <c r="O32" s="86"/>
-      <c r="P32" s="86"/>
-      <c r="Q32" s="86"/>
-      <c r="R32" s="86"/>
-      <c r="S32" s="86"/>
-      <c r="T32" s="86"/>
-      <c r="U32" s="86"/>
-      <c r="V32" s="86"/>
+      <c r="G32" s="95"/>
+      <c r="H32" s="95"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="95"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="95"/>
+      <c r="P32" s="95"/>
+      <c r="Q32" s="95"/>
+      <c r="R32" s="95"/>
+      <c r="S32" s="95"/>
+      <c r="T32" s="95"/>
+      <c r="U32" s="95"/>
+      <c r="V32" s="95"/>
     </row>
     <row r="33" spans="1:22">
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="86"/>
-      <c r="M33" s="86"/>
-      <c r="N33" s="86"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="86"/>
-      <c r="Q33" s="86"/>
-      <c r="R33" s="86"/>
-      <c r="S33" s="86"/>
-      <c r="T33" s="86"/>
-      <c r="U33" s="86"/>
-      <c r="V33" s="86"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="95"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="95"/>
+      <c r="O33" s="95"/>
+      <c r="P33" s="95"/>
+      <c r="Q33" s="95"/>
+      <c r="R33" s="95"/>
+      <c r="S33" s="95"/>
+      <c r="T33" s="95"/>
+      <c r="U33" s="95"/>
+      <c r="V33" s="95"/>
     </row>
     <row r="34" spans="1:22">
       <c r="B34" s="1" t="s">
@@ -11906,21 +12842,21 @@
       <c r="E338" s="59" t="s">
         <v>279</v>
       </c>
-      <c r="F338" s="89" t="s">
+      <c r="F338" s="96" t="s">
         <v>323</v>
       </c>
-      <c r="G338" s="90"/>
-      <c r="H338" s="90"/>
-      <c r="I338" s="90"/>
-      <c r="J338" s="90"/>
-      <c r="K338" s="90"/>
-      <c r="L338" s="90"/>
-      <c r="M338" s="90"/>
-      <c r="N338" s="90"/>
-      <c r="O338" s="90"/>
-      <c r="P338" s="90"/>
-      <c r="Q338" s="90"/>
-      <c r="R338" s="91"/>
+      <c r="G338" s="97"/>
+      <c r="H338" s="97"/>
+      <c r="I338" s="97"/>
+      <c r="J338" s="97"/>
+      <c r="K338" s="97"/>
+      <c r="L338" s="97"/>
+      <c r="M338" s="97"/>
+      <c r="N338" s="97"/>
+      <c r="O338" s="97"/>
+      <c r="P338" s="97"/>
+      <c r="Q338" s="97"/>
+      <c r="R338" s="98"/>
     </row>
     <row r="339" spans="2:18" ht="15">
       <c r="B339" s="12" t="s">
@@ -11931,21 +12867,21 @@
       <c r="E339" s="60" t="s">
         <v>281</v>
       </c>
-      <c r="F339" s="96" t="s">
+      <c r="F339" s="92" t="s">
         <v>322</v>
       </c>
-      <c r="G339" s="97"/>
-      <c r="H339" s="97"/>
-      <c r="I339" s="97"/>
-      <c r="J339" s="97"/>
-      <c r="K339" s="97"/>
-      <c r="L339" s="97"/>
-      <c r="M339" s="97"/>
-      <c r="N339" s="97"/>
-      <c r="O339" s="97"/>
-      <c r="P339" s="97"/>
-      <c r="Q339" s="97"/>
-      <c r="R339" s="98"/>
+      <c r="G339" s="93"/>
+      <c r="H339" s="93"/>
+      <c r="I339" s="93"/>
+      <c r="J339" s="93"/>
+      <c r="K339" s="93"/>
+      <c r="L339" s="93"/>
+      <c r="M339" s="93"/>
+      <c r="N339" s="93"/>
+      <c r="O339" s="93"/>
+      <c r="P339" s="93"/>
+      <c r="Q339" s="93"/>
+      <c r="R339" s="94"/>
     </row>
     <row r="340" spans="2:18" ht="15">
       <c r="B340" s="12" t="s">
@@ -11956,21 +12892,21 @@
       <c r="E340" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="F340" s="95" t="s">
+      <c r="F340" s="89" t="s">
         <v>324</v>
       </c>
-      <c r="G340" s="87"/>
-      <c r="H340" s="87"/>
-      <c r="I340" s="87"/>
-      <c r="J340" s="87"/>
-      <c r="K340" s="87"/>
-      <c r="L340" s="87"/>
-      <c r="M340" s="87"/>
-      <c r="N340" s="87"/>
-      <c r="O340" s="87"/>
-      <c r="P340" s="87"/>
-      <c r="Q340" s="87"/>
-      <c r="R340" s="88"/>
+      <c r="G340" s="90"/>
+      <c r="H340" s="90"/>
+      <c r="I340" s="90"/>
+      <c r="J340" s="90"/>
+      <c r="K340" s="90"/>
+      <c r="L340" s="90"/>
+      <c r="M340" s="90"/>
+      <c r="N340" s="90"/>
+      <c r="O340" s="90"/>
+      <c r="P340" s="90"/>
+      <c r="Q340" s="90"/>
+      <c r="R340" s="91"/>
     </row>
     <row r="341" spans="2:18" ht="15">
       <c r="B341" s="12" t="s">
@@ -12006,21 +12942,21 @@
       <c r="E342" s="61" t="s">
         <v>288</v>
       </c>
-      <c r="F342" s="95" t="s">
+      <c r="F342" s="89" t="s">
         <v>325</v>
       </c>
-      <c r="G342" s="87"/>
-      <c r="H342" s="87"/>
-      <c r="I342" s="87"/>
-      <c r="J342" s="87"/>
-      <c r="K342" s="87"/>
-      <c r="L342" s="87"/>
-      <c r="M342" s="87"/>
-      <c r="N342" s="87"/>
-      <c r="O342" s="87"/>
-      <c r="P342" s="87"/>
-      <c r="Q342" s="87"/>
-      <c r="R342" s="88"/>
+      <c r="G342" s="90"/>
+      <c r="H342" s="90"/>
+      <c r="I342" s="90"/>
+      <c r="J342" s="90"/>
+      <c r="K342" s="90"/>
+      <c r="L342" s="90"/>
+      <c r="M342" s="90"/>
+      <c r="N342" s="90"/>
+      <c r="O342" s="90"/>
+      <c r="P342" s="90"/>
+      <c r="Q342" s="90"/>
+      <c r="R342" s="91"/>
     </row>
     <row r="343" spans="2:18" ht="15">
       <c r="B343" s="12" t="s">
@@ -12031,21 +12967,21 @@
       <c r="E343" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="F343" s="96" t="s">
+      <c r="F343" s="92" t="s">
         <v>326</v>
       </c>
-      <c r="G343" s="97"/>
-      <c r="H343" s="97"/>
-      <c r="I343" s="97"/>
-      <c r="J343" s="97"/>
-      <c r="K343" s="97"/>
-      <c r="L343" s="97"/>
-      <c r="M343" s="97"/>
-      <c r="N343" s="97"/>
-      <c r="O343" s="97"/>
-      <c r="P343" s="97"/>
-      <c r="Q343" s="97"/>
-      <c r="R343" s="98"/>
+      <c r="G343" s="93"/>
+      <c r="H343" s="93"/>
+      <c r="I343" s="93"/>
+      <c r="J343" s="93"/>
+      <c r="K343" s="93"/>
+      <c r="L343" s="93"/>
+      <c r="M343" s="93"/>
+      <c r="N343" s="93"/>
+      <c r="O343" s="93"/>
+      <c r="P343" s="93"/>
+      <c r="Q343" s="93"/>
+      <c r="R343" s="94"/>
     </row>
     <row r="344" spans="2:18" ht="15">
       <c r="B344" s="12" t="s">
@@ -12081,21 +13017,21 @@
       <c r="E345" s="60" t="s">
         <v>295</v>
       </c>
-      <c r="F345" s="96" t="s">
+      <c r="F345" s="92" t="s">
         <v>327</v>
       </c>
-      <c r="G345" s="97"/>
-      <c r="H345" s="97"/>
-      <c r="I345" s="97"/>
-      <c r="J345" s="97"/>
-      <c r="K345" s="97"/>
-      <c r="L345" s="97"/>
-      <c r="M345" s="97"/>
-      <c r="N345" s="97"/>
-      <c r="O345" s="97"/>
-      <c r="P345" s="97"/>
-      <c r="Q345" s="97"/>
-      <c r="R345" s="98"/>
+      <c r="G345" s="93"/>
+      <c r="H345" s="93"/>
+      <c r="I345" s="93"/>
+      <c r="J345" s="93"/>
+      <c r="K345" s="93"/>
+      <c r="L345" s="93"/>
+      <c r="M345" s="93"/>
+      <c r="N345" s="93"/>
+      <c r="O345" s="93"/>
+      <c r="P345" s="93"/>
+      <c r="Q345" s="93"/>
+      <c r="R345" s="94"/>
     </row>
     <row r="346" spans="2:18" ht="15">
       <c r="B346" s="12" t="s">
@@ -12106,21 +13042,21 @@
       <c r="E346" s="61" t="s">
         <v>297</v>
       </c>
-      <c r="F346" s="95" t="s">
+      <c r="F346" s="89" t="s">
         <v>328</v>
       </c>
-      <c r="G346" s="87"/>
-      <c r="H346" s="87"/>
-      <c r="I346" s="87"/>
-      <c r="J346" s="87"/>
-      <c r="K346" s="87"/>
-      <c r="L346" s="87"/>
-      <c r="M346" s="87"/>
-      <c r="N346" s="87"/>
-      <c r="O346" s="87"/>
-      <c r="P346" s="87"/>
-      <c r="Q346" s="87"/>
-      <c r="R346" s="88"/>
+      <c r="G346" s="90"/>
+      <c r="H346" s="90"/>
+      <c r="I346" s="90"/>
+      <c r="J346" s="90"/>
+      <c r="K346" s="90"/>
+      <c r="L346" s="90"/>
+      <c r="M346" s="90"/>
+      <c r="N346" s="90"/>
+      <c r="O346" s="90"/>
+      <c r="P346" s="90"/>
+      <c r="Q346" s="90"/>
+      <c r="R346" s="91"/>
     </row>
     <row r="347" spans="2:18" ht="15">
       <c r="B347" s="12" t="s">
@@ -12131,21 +13067,21 @@
       <c r="E347" s="60" t="s">
         <v>299</v>
       </c>
-      <c r="F347" s="96" t="s">
+      <c r="F347" s="92" t="s">
         <v>329</v>
       </c>
-      <c r="G347" s="97"/>
-      <c r="H347" s="97"/>
-      <c r="I347" s="97"/>
-      <c r="J347" s="97"/>
-      <c r="K347" s="97"/>
-      <c r="L347" s="97"/>
-      <c r="M347" s="97"/>
-      <c r="N347" s="97"/>
-      <c r="O347" s="97"/>
-      <c r="P347" s="97"/>
-      <c r="Q347" s="97"/>
-      <c r="R347" s="98"/>
+      <c r="G347" s="93"/>
+      <c r="H347" s="93"/>
+      <c r="I347" s="93"/>
+      <c r="J347" s="93"/>
+      <c r="K347" s="93"/>
+      <c r="L347" s="93"/>
+      <c r="M347" s="93"/>
+      <c r="N347" s="93"/>
+      <c r="O347" s="93"/>
+      <c r="P347" s="93"/>
+      <c r="Q347" s="93"/>
+      <c r="R347" s="94"/>
     </row>
     <row r="348" spans="2:18" ht="15">
       <c r="B348" s="12" t="s">
@@ -12156,21 +13092,21 @@
       <c r="E348" s="64" t="s">
         <v>301</v>
       </c>
-      <c r="F348" s="87" t="s">
+      <c r="F348" s="90" t="s">
         <v>302</v>
       </c>
-      <c r="G348" s="87"/>
-      <c r="H348" s="87"/>
-      <c r="I348" s="87"/>
-      <c r="J348" s="87"/>
-      <c r="K348" s="87"/>
-      <c r="L348" s="87"/>
-      <c r="M348" s="87"/>
-      <c r="N348" s="87"/>
-      <c r="O348" s="87"/>
-      <c r="P348" s="87"/>
-      <c r="Q348" s="87"/>
-      <c r="R348" s="88"/>
+      <c r="G348" s="90"/>
+      <c r="H348" s="90"/>
+      <c r="I348" s="90"/>
+      <c r="J348" s="90"/>
+      <c r="K348" s="90"/>
+      <c r="L348" s="90"/>
+      <c r="M348" s="90"/>
+      <c r="N348" s="90"/>
+      <c r="O348" s="90"/>
+      <c r="P348" s="90"/>
+      <c r="Q348" s="90"/>
+      <c r="R348" s="91"/>
     </row>
     <row r="349" spans="2:18" ht="15">
       <c r="B349" s="12" t="s">
@@ -12206,21 +13142,21 @@
       <c r="E350" s="65" t="s">
         <v>306</v>
       </c>
-      <c r="F350" s="92" t="s">
+      <c r="F350" s="86" t="s">
         <v>307</v>
       </c>
-      <c r="G350" s="93"/>
-      <c r="H350" s="93"/>
-      <c r="I350" s="93"/>
-      <c r="J350" s="93"/>
-      <c r="K350" s="93"/>
-      <c r="L350" s="93"/>
-      <c r="M350" s="93"/>
-      <c r="N350" s="93"/>
-      <c r="O350" s="93"/>
-      <c r="P350" s="93"/>
-      <c r="Q350" s="93"/>
-      <c r="R350" s="94"/>
+      <c r="G350" s="87"/>
+      <c r="H350" s="87"/>
+      <c r="I350" s="87"/>
+      <c r="J350" s="87"/>
+      <c r="K350" s="87"/>
+      <c r="L350" s="87"/>
+      <c r="M350" s="87"/>
+      <c r="N350" s="87"/>
+      <c r="O350" s="87"/>
+      <c r="P350" s="87"/>
+      <c r="Q350" s="87"/>
+      <c r="R350" s="88"/>
     </row>
     <row r="351" spans="2:18">
       <c r="C351" s="1" t="s">
@@ -12625,6 +13561,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="F28:V29"/>
+    <mergeCell ref="F30:V31"/>
+    <mergeCell ref="F32:V33"/>
+    <mergeCell ref="F348:R348"/>
+    <mergeCell ref="F338:R338"/>
     <mergeCell ref="F350:R350"/>
     <mergeCell ref="F342:R342"/>
     <mergeCell ref="F339:R339"/>
@@ -12633,12 +13575,6 @@
     <mergeCell ref="F345:R345"/>
     <mergeCell ref="F346:R346"/>
     <mergeCell ref="F347:R347"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="F28:V29"/>
-    <mergeCell ref="F30:V31"/>
-    <mergeCell ref="F32:V33"/>
-    <mergeCell ref="F348:R348"/>
-    <mergeCell ref="F338:R338"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q14" r:id="rId1" xr:uid="{739BC0F6-DDEA-409E-BAA0-CED0EC3FAC10}"/>
@@ -20633,8 +21569,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="F28:R28 F34:R34 P29:Q29 P30:Q30 P31:Q31 P32:Q32 P33:Q33 F38:R38 P35:Q35 P36:Q36 P37:Q37 P39:Q39 AM87:AP87" formula="1"/>
-    <ignoredError sqref="R31:R33 AM31:AP34 AM39:AP40 AM42:AP42 F75:U79" formulaRange="1"/>
+    <ignoredError sqref="R31:R33 AM31:AP34 AM39:AP40 AM42:AP42 F75:U79 J39" formulaRange="1"/>
     <ignoredError sqref="AM41:AP41" formula="1" formulaRange="1"/>
+    <ignoredError sqref="BA63" twoDigitTextYear="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -25342,350 +26279,404 @@
       </c>
     </row>
     <row r="3" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="101" t="s">
         <v>416</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
       <c r="E3" s="68"/>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="102" t="s">
         <v>417</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
     </row>
     <row r="4" spans="2:8" ht="17.25">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="103" t="s">
         <v>418</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
       <c r="E4" s="68"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
     </row>
     <row r="5" spans="2:8" ht="17.25">
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
       <c r="E5" s="68"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B6" s="104" t="s">
+      <c r="B6" s="101" t="s">
         <v>419</v>
       </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
       <c r="E6" s="68"/>
-      <c r="F6" s="101" t="s">
+      <c r="F6" s="102" t="s">
         <v>420</v>
       </c>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
     </row>
     <row r="7" spans="2:8" ht="17.25">
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="103" t="s">
         <v>421</v>
       </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
       <c r="E7" s="68"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
     </row>
     <row r="8" spans="2:8" ht="17.25">
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
       <c r="E8" s="68"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
     </row>
     <row r="9" spans="2:8" ht="18" thickBot="1">
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="101" t="s">
         <v>422</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
       <c r="E9" s="68"/>
-      <c r="F9" s="101" t="s">
+      <c r="F9" s="102" t="s">
         <v>423</v>
       </c>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
     </row>
     <row r="10" spans="2:8" ht="17.25">
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="103" t="s">
         <v>424</v>
       </c>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
       <c r="E10" s="68"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
     </row>
     <row r="11" spans="2:8" ht="17.25">
-      <c r="B11" s="103"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
       <c r="E11" s="68"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
     </row>
     <row r="12" spans="2:8" ht="18" thickBot="1">
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="101" t="s">
         <v>425</v>
       </c>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
       <c r="E12" s="68"/>
-      <c r="F12" s="101" t="s">
+      <c r="F12" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G12" s="101"/>
-      <c r="H12" s="101"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
     </row>
     <row r="13" spans="2:8" ht="17.25">
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="103" t="s">
         <v>427</v>
       </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
     </row>
     <row r="14" spans="2:8" ht="17.25">
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
       <c r="E14" s="68"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="100"/>
     </row>
     <row r="15" spans="2:8" ht="18" thickBot="1">
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="101" t="s">
         <v>428</v>
       </c>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
       <c r="E15" s="68"/>
-      <c r="F15" s="101" t="s">
+      <c r="F15" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
     </row>
     <row r="16" spans="2:8" ht="17.25">
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="103" t="s">
         <v>429</v>
       </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
     </row>
     <row r="17" spans="2:8" ht="17.25">
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
       <c r="E17" s="68"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
     </row>
     <row r="18" spans="2:8" ht="18" thickBot="1">
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="101" t="s">
         <v>430</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
       <c r="E18" s="68"/>
-      <c r="F18" s="101" t="s">
+      <c r="F18" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G18" s="101"/>
-      <c r="H18" s="101"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
     </row>
     <row r="19" spans="2:8" ht="17.25">
-      <c r="B19" s="102" t="s">
+      <c r="B19" s="103" t="s">
         <v>431</v>
       </c>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
       <c r="E19" s="68"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
     </row>
     <row r="20" spans="2:8" ht="17.25">
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
       <c r="E20" s="68"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
     </row>
     <row r="21" spans="2:8" ht="18" thickBot="1">
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="101" t="s">
         <v>432</v>
       </c>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
       <c r="E21" s="68"/>
-      <c r="F21" s="101" t="s">
+      <c r="F21" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G21" s="101"/>
-      <c r="H21" s="101"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
     </row>
     <row r="22" spans="2:8" ht="17.25">
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="103" t="s">
         <v>433</v>
       </c>
-      <c r="C22" s="102"/>
-      <c r="D22" s="102"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
       <c r="E22" s="68"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="100"/>
     </row>
     <row r="23" spans="2:8" ht="17.25">
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
       <c r="E23" s="68"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
     </row>
     <row r="24" spans="2:8" ht="18" thickBot="1">
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="101" t="s">
         <v>434</v>
       </c>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
       <c r="E24" s="68"/>
-      <c r="F24" s="101" t="s">
+      <c r="F24" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G24" s="101"/>
-      <c r="H24" s="101"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
     </row>
     <row r="25" spans="2:8" ht="17.25">
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="103" t="s">
         <v>435</v>
       </c>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
       <c r="E25" s="68"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
     </row>
     <row r="26" spans="2:8" ht="17.25">
-      <c r="B26" s="103"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="100"/>
       <c r="E26" s="68"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
+      <c r="F26" s="100"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
     </row>
     <row r="27" spans="2:8" ht="18" thickBot="1">
-      <c r="B27" s="104" t="s">
+      <c r="B27" s="101" t="s">
         <v>436</v>
       </c>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
       <c r="E27" s="68"/>
-      <c r="F27" s="101" t="s">
+      <c r="F27" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G27" s="101"/>
-      <c r="H27" s="101"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="102"/>
     </row>
     <row r="28" spans="2:8" ht="17.25">
-      <c r="B28" s="102" t="s">
+      <c r="B28" s="103" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="102"/>
-      <c r="D28" s="102"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
       <c r="E28" s="68"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="103"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="100"/>
     </row>
     <row r="29" spans="2:8" ht="17.25">
-      <c r="B29" s="103"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="103"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="100"/>
+      <c r="D29" s="100"/>
       <c r="E29" s="68"/>
-      <c r="F29" s="103"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="100"/>
     </row>
     <row r="30" spans="2:8" ht="18" thickBot="1">
-      <c r="B30" s="104" t="s">
+      <c r="B30" s="101" t="s">
         <v>438</v>
       </c>
-      <c r="C30" s="104"/>
-      <c r="D30" s="104"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="101"/>
       <c r="E30" s="68"/>
-      <c r="F30" s="101" t="s">
+      <c r="F30" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G30" s="101"/>
-      <c r="H30" s="101"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="102"/>
     </row>
     <row r="31" spans="2:8" ht="17.25">
-      <c r="B31" s="102" t="s">
+      <c r="B31" s="103" t="s">
         <v>439</v>
       </c>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="103"/>
       <c r="E31" s="68"/>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
     </row>
     <row r="32" spans="2:8" ht="17.25">
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
+      <c r="B32" s="100"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="100"/>
       <c r="E32" s="68"/>
-      <c r="F32" s="103"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
     </row>
     <row r="33" spans="2:8" ht="17.25">
-      <c r="B33" s="100" t="s">
+      <c r="B33" s="104" t="s">
         <v>440</v>
       </c>
-      <c r="C33" s="100"/>
-      <c r="D33" s="100"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="104"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="101" t="s">
+      <c r="F33" s="102" t="s">
         <v>426</v>
       </c>
-      <c r="G33" s="101"/>
-      <c r="H33" s="101"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="B6:D6"/>
@@ -25694,60 +26685,6 @@
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="F4:H4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="F32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
